--- a/output/yearly_population_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_89_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4848</v>
+        <v>5541</v>
       </c>
       <c r="C2" t="n">
-        <v>9398</v>
+        <v>9151</v>
       </c>
       <c r="D2" t="n">
-        <v>25688</v>
+        <v>32394</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2854</v>
+        <v>3510</v>
       </c>
       <c r="C3" t="n">
-        <v>6722</v>
+        <v>6322</v>
       </c>
       <c r="D3" t="n">
-        <v>11807</v>
+        <v>13879</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>2509</v>
       </c>
       <c r="C4" t="n">
-        <v>5104</v>
+        <v>4761</v>
       </c>
       <c r="D4" t="n">
-        <v>6270</v>
+        <v>8274</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1703</v>
+        <v>1599</v>
       </c>
       <c r="C5" t="n">
-        <v>5622</v>
+        <v>4513</v>
       </c>
       <c r="D5" t="n">
-        <v>2419</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>990</v>
+        <v>912</v>
       </c>
       <c r="C6" t="n">
-        <v>4628</v>
+        <v>3305</v>
       </c>
       <c r="D6" t="n">
-        <v>1079</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="C7" t="n">
-        <v>2819</v>
+        <v>1993</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>1250</v>
+        <v>958</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -926,7 +926,7 @@
         <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>59</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5910</v>
+        <v>6532</v>
       </c>
       <c r="C2" t="n">
-        <v>11925</v>
+        <v>16391</v>
       </c>
       <c r="D2" t="n">
-        <v>20757</v>
+        <v>35602</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3034</v>
+        <v>3581</v>
       </c>
       <c r="C3" t="n">
-        <v>6953</v>
+        <v>6682</v>
       </c>
       <c r="D3" t="n">
-        <v>12809</v>
+        <v>15464</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>2530</v>
       </c>
       <c r="C4" t="n">
-        <v>5678</v>
+        <v>5396</v>
       </c>
       <c r="D4" t="n">
-        <v>6869</v>
+        <v>8937</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1786</v>
+        <v>1749</v>
       </c>
       <c r="C5" t="n">
-        <v>5222</v>
+        <v>4487</v>
       </c>
       <c r="D5" t="n">
-        <v>2936</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1167</v>
+        <v>1092</v>
       </c>
       <c r="C6" t="n">
-        <v>5013</v>
+        <v>3806</v>
       </c>
       <c r="D6" t="n">
-        <v>1247</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>561</v>
       </c>
       <c r="C7" t="n">
-        <v>3552</v>
+        <v>2538</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C8" t="n">
-        <v>1895</v>
+        <v>1384</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>753</v>
+        <v>635</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1273,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>64</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6121</v>
+        <v>6952</v>
       </c>
       <c r="C2" t="n">
-        <v>14204</v>
+        <v>17652</v>
       </c>
       <c r="D2" t="n">
-        <v>30058</v>
+        <v>31915</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>3855</v>
       </c>
       <c r="C3" t="n">
-        <v>7906</v>
+        <v>9361</v>
       </c>
       <c r="D3" t="n">
-        <v>12942</v>
+        <v>16890</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2173</v>
+        <v>2508</v>
       </c>
       <c r="C4" t="n">
-        <v>6031</v>
+        <v>5775</v>
       </c>
       <c r="D4" t="n">
-        <v>7515</v>
+        <v>9519</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1758</v>
+        <v>1826</v>
       </c>
       <c r="C5" t="n">
-        <v>5297</v>
+        <v>4725</v>
       </c>
       <c r="D5" t="n">
-        <v>3347</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1294</v>
+        <v>1241</v>
       </c>
       <c r="C6" t="n">
-        <v>5002</v>
+        <v>4047</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="C7" t="n">
-        <v>4074</v>
+        <v>3009</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>891</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C8" t="n">
-        <v>2492</v>
+        <v>1810</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>1166</v>
+        <v>913</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5704</v>
+        <v>6455</v>
       </c>
       <c r="C2" t="n">
-        <v>9999</v>
+        <v>12144</v>
       </c>
       <c r="D2" t="n">
-        <v>24667</v>
+        <v>26342</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3910</v>
+        <v>4534</v>
       </c>
       <c r="C3" t="n">
-        <v>11558</v>
+        <v>13402</v>
       </c>
       <c r="D3" t="n">
-        <v>14111</v>
+        <v>18327</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1624</v>
+        <v>1687</v>
       </c>
       <c r="C4" t="n">
-        <v>8269</v>
+        <v>7640</v>
       </c>
       <c r="D4" t="n">
-        <v>7251</v>
+        <v>9432</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1195</v>
+        <v>1146</v>
       </c>
       <c r="C5" t="n">
-        <v>4901</v>
+        <v>3966</v>
       </c>
       <c r="D5" t="n">
-        <v>2295</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>672</v>
+        <v>632</v>
       </c>
       <c r="C6" t="n">
-        <v>3992</v>
+        <v>2948</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>2442</v>
+        <v>1773</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>1142</v>
+        <v>894</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3466</v>
+        <v>3939</v>
       </c>
       <c r="C2" t="n">
-        <v>4859</v>
+        <v>5617</v>
       </c>
       <c r="D2" t="n">
-        <v>17740</v>
+        <v>18394</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4011</v>
+        <v>4602</v>
       </c>
       <c r="C3" t="n">
-        <v>9911</v>
+        <v>11676</v>
       </c>
       <c r="D3" t="n">
-        <v>14671</v>
+        <v>18537</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2164</v>
+        <v>2367</v>
       </c>
       <c r="C4" t="n">
-        <v>9787</v>
+        <v>10300</v>
       </c>
       <c r="D4" t="n">
-        <v>8157</v>
+        <v>10516</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="C5" t="n">
-        <v>6359</v>
+        <v>5555</v>
       </c>
       <c r="D5" t="n">
-        <v>2840</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="C6" t="n">
-        <v>4494</v>
+        <v>3470</v>
       </c>
       <c r="D6" t="n">
-        <v>884</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>3051</v>
+        <v>2210</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1494</v>
+        <v>1167</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>481</v>
+        <v>438</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>165</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3028</v>
+        <v>3682</v>
       </c>
       <c r="C2" t="n">
-        <v>10657</v>
+        <v>6173</v>
       </c>
       <c r="D2" t="n">
-        <v>16411</v>
+        <v>18169</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3187</v>
+        <v>3644</v>
       </c>
       <c r="C3" t="n">
-        <v>6796</v>
+        <v>7851</v>
       </c>
       <c r="D3" t="n">
-        <v>14102</v>
+        <v>17271</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2528</v>
+        <v>2818</v>
       </c>
       <c r="C4" t="n">
-        <v>9641</v>
+        <v>10746</v>
       </c>
       <c r="D4" t="n">
-        <v>8972</v>
+        <v>11505</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1468</v>
+        <v>1532</v>
       </c>
       <c r="C5" t="n">
-        <v>7773</v>
+        <v>7679</v>
       </c>
       <c r="D5" t="n">
-        <v>3570</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>907</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>5301</v>
+        <v>4338</v>
       </c>
       <c r="D6" t="n">
-        <v>1153</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="C7" t="n">
-        <v>3673</v>
+        <v>2761</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>2088</v>
+        <v>1586</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>857</v>
+        <v>706</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1841</v>
+        <v>2230</v>
       </c>
       <c r="C2" t="n">
-        <v>5154</v>
+        <v>2981</v>
       </c>
       <c r="D2" t="n">
-        <v>11504</v>
+        <v>12682</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3043</v>
+        <v>3527</v>
       </c>
       <c r="C3" t="n">
-        <v>7846</v>
+        <v>7025</v>
       </c>
       <c r="D3" t="n">
-        <v>14026</v>
+        <v>16977</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2778</v>
+        <v>3084</v>
       </c>
       <c r="C4" t="n">
-        <v>9492</v>
+        <v>10740</v>
       </c>
       <c r="D4" t="n">
-        <v>9641</v>
+        <v>12252</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1544</v>
+        <v>1570</v>
       </c>
       <c r="C5" t="n">
-        <v>9504</v>
+        <v>9437</v>
       </c>
       <c r="D5" t="n">
-        <v>3752</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>6227</v>
+        <v>5168</v>
       </c>
       <c r="D6" t="n">
-        <v>1129</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>3828</v>
+        <v>2873</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1433</v>
+        <v>1158</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1999</v>
+        <v>2217</v>
       </c>
       <c r="C2" t="n">
-        <v>6927</v>
+        <v>7912</v>
       </c>
       <c r="D2" t="n">
-        <v>10422</v>
+        <v>16937</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2181</v>
+        <v>2576</v>
       </c>
       <c r="C3" t="n">
-        <v>5971</v>
+        <v>4719</v>
       </c>
       <c r="D3" t="n">
-        <v>12783</v>
+        <v>15313</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2547</v>
+        <v>2876</v>
       </c>
       <c r="C4" t="n">
-        <v>8551</v>
+        <v>8840</v>
       </c>
       <c r="D4" t="n">
-        <v>10021</v>
+        <v>12605</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1803</v>
+        <v>1908</v>
       </c>
       <c r="C5" t="n">
-        <v>9392</v>
+        <v>9894</v>
       </c>
       <c r="D5" t="n">
-        <v>4485</v>
+        <v>5956</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="C6" t="n">
-        <v>7554</v>
+        <v>6894</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C7" t="n">
-        <v>4818</v>
+        <v>3805</v>
       </c>
       <c r="D7" t="n">
-        <v>616</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2281</v>
+        <v>1768</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>566</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1366</v>
+        <v>1553</v>
       </c>
       <c r="C2" t="n">
-        <v>5479</v>
+        <v>4296</v>
       </c>
       <c r="D2" t="n">
-        <v>7965</v>
+        <v>12627</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1865</v>
+        <v>2165</v>
       </c>
       <c r="C3" t="n">
-        <v>5822</v>
+        <v>5439</v>
       </c>
       <c r="D3" t="n">
-        <v>11843</v>
+        <v>14686</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2234</v>
+        <v>2550</v>
       </c>
       <c r="C4" t="n">
-        <v>7628</v>
+        <v>7243</v>
       </c>
       <c r="D4" t="n">
-        <v>10157</v>
+        <v>12680</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1938</v>
+        <v>2083</v>
       </c>
       <c r="C5" t="n">
-        <v>9184</v>
+        <v>9703</v>
       </c>
       <c r="D5" t="n">
-        <v>5019</v>
+        <v>6591</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C6" t="n">
-        <v>8405</v>
+        <v>8051</v>
       </c>
       <c r="D6" t="n">
-        <v>1719</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>5763</v>
+        <v>4760</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2867</v>
+        <v>2235</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>722</v>
+        <v>621</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +3386,7 @@
         <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2424</v>
+        <v>3326</v>
       </c>
       <c r="C2" t="n">
-        <v>20776</v>
+        <v>4810</v>
       </c>
       <c r="D2" t="n">
-        <v>7662</v>
+        <v>18579</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1431</v>
+        <v>1652</v>
       </c>
       <c r="C3" t="n">
-        <v>5082</v>
+        <v>4471</v>
       </c>
       <c r="D3" t="n">
-        <v>10669</v>
+        <v>13538</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1834</v>
+        <v>2104</v>
       </c>
       <c r="C4" t="n">
-        <v>6741</v>
+        <v>6364</v>
       </c>
       <c r="D4" t="n">
-        <v>10074</v>
+        <v>12564</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1880</v>
+        <v>2061</v>
       </c>
       <c r="C5" t="n">
-        <v>8395</v>
+        <v>8556</v>
       </c>
       <c r="D5" t="n">
-        <v>5459</v>
+        <v>7087</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1243</v>
+        <v>1281</v>
       </c>
       <c r="C6" t="n">
-        <v>8621</v>
+        <v>8589</v>
       </c>
       <c r="D6" t="n">
-        <v>2108</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" t="n">
-        <v>6692</v>
+        <v>5919</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>3858</v>
+        <v>3097</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1373</v>
+        <v>1111</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5602</v>
+        <v>4607</v>
       </c>
       <c r="C2" t="n">
-        <v>10760</v>
+        <v>9511</v>
       </c>
       <c r="D2" t="n">
-        <v>8620</v>
+        <v>21436</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1770</v>
+        <v>2429</v>
       </c>
       <c r="C2" t="n">
-        <v>12299</v>
+        <v>2847</v>
       </c>
       <c r="D2" t="n">
-        <v>5700</v>
+        <v>13822</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2018</v>
+        <v>2346</v>
       </c>
       <c r="C3" t="n">
-        <v>8874</v>
+        <v>5010</v>
       </c>
       <c r="D3" t="n">
-        <v>11444</v>
+        <v>15001</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2657</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>9617</v>
+        <v>9266</v>
       </c>
       <c r="D4" t="n">
-        <v>10207</v>
+        <v>12797</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>1202</v>
       </c>
       <c r="C5" t="n">
-        <v>12166</v>
+        <v>12241</v>
       </c>
       <c r="D5" t="n">
-        <v>4984</v>
+        <v>6482</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C6" t="n">
-        <v>8078</v>
+        <v>7315</v>
       </c>
       <c r="D6" t="n">
-        <v>1698</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>3780</v>
+        <v>3035</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1345</v>
+        <v>1088</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
         <v>133</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6730</v>
+        <v>6662</v>
       </c>
       <c r="C2" t="n">
-        <v>10213</v>
+        <v>5323</v>
       </c>
       <c r="D2" t="n">
-        <v>13399</v>
+        <v>23998</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2380</v>
+        <v>1958</v>
       </c>
       <c r="C3" t="n">
-        <v>5423</v>
+        <v>4793</v>
       </c>
       <c r="D3" t="n">
-        <v>2087</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4619</v>
+        <v>4592</v>
       </c>
       <c r="C2" t="n">
-        <v>13423</v>
+        <v>6588</v>
       </c>
       <c r="D2" t="n">
-        <v>17068</v>
+        <v>21300</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3739</v>
+        <v>3535</v>
       </c>
       <c r="C3" t="n">
-        <v>7014</v>
+        <v>4392</v>
       </c>
       <c r="D3" t="n">
-        <v>3833</v>
+        <v>7247</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1068</v>
+        <v>885</v>
       </c>
       <c r="C4" t="n">
-        <v>3221</v>
+        <v>2852</v>
       </c>
       <c r="D4" t="n">
-        <v>1601</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5388</v>
+        <v>4465</v>
       </c>
       <c r="C2" t="n">
-        <v>8298</v>
+        <v>7913</v>
       </c>
       <c r="D2" t="n">
-        <v>22416</v>
+        <v>33339</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3435</v>
+        <v>3336</v>
       </c>
       <c r="C3" t="n">
-        <v>9056</v>
+        <v>4827</v>
       </c>
       <c r="D3" t="n">
-        <v>5674</v>
+        <v>8973</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2043</v>
+        <v>1875</v>
       </c>
       <c r="C4" t="n">
-        <v>5235</v>
+        <v>3622</v>
       </c>
       <c r="D4" t="n">
-        <v>1980</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>490</v>
+        <v>416</v>
       </c>
       <c r="C5" t="n">
-        <v>1857</v>
+        <v>1657</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5754</v>
+        <v>4910</v>
       </c>
       <c r="C2" t="n">
-        <v>8598</v>
+        <v>8909</v>
       </c>
       <c r="D2" t="n">
-        <v>29011</v>
+        <v>28798</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3563</v>
+        <v>3177</v>
       </c>
       <c r="C3" t="n">
-        <v>7563</v>
+        <v>5566</v>
       </c>
       <c r="D3" t="n">
-        <v>7819</v>
+        <v>12044</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>2186</v>
       </c>
       <c r="C4" t="n">
-        <v>7143</v>
+        <v>4148</v>
       </c>
       <c r="D4" t="n">
-        <v>2593</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1023</v>
+        <v>937</v>
       </c>
       <c r="C5" t="n">
-        <v>3519</v>
+        <v>2641</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="C6" t="n">
-        <v>1075</v>
+        <v>978</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
         <v>666</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
         <v>471</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5631</v>
+        <v>5997</v>
       </c>
       <c r="C2" t="n">
-        <v>7068</v>
+        <v>6239</v>
       </c>
       <c r="D2" t="n">
-        <v>22974</v>
+        <v>24247</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3341</v>
+        <v>2904</v>
       </c>
       <c r="C3" t="n">
-        <v>6622</v>
+        <v>5936</v>
       </c>
       <c r="D3" t="n">
-        <v>9707</v>
+        <v>12929</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1814</v>
+        <v>1644</v>
       </c>
       <c r="C4" t="n">
-        <v>5965</v>
+        <v>4021</v>
       </c>
       <c r="D4" t="n">
-        <v>2955</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>856</v>
+        <v>804</v>
       </c>
       <c r="C5" t="n">
-        <v>3916</v>
+        <v>2467</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>1513</v>
+        <v>1212</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4432</v>
+        <v>4878</v>
       </c>
       <c r="C2" t="n">
-        <v>4809</v>
+        <v>5542</v>
       </c>
       <c r="D2" t="n">
-        <v>19579</v>
+        <v>20063</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3692</v>
+        <v>3682</v>
       </c>
       <c r="C3" t="n">
-        <v>5921</v>
+        <v>5259</v>
       </c>
       <c r="D3" t="n">
-        <v>11221</v>
+        <v>13878</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>1986</v>
       </c>
       <c r="C4" t="n">
-        <v>6231</v>
+        <v>5038</v>
       </c>
       <c r="D4" t="n">
-        <v>4226</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1184</v>
+        <v>1079</v>
       </c>
       <c r="C5" t="n">
-        <v>5014</v>
+        <v>3325</v>
       </c>
       <c r="D5" t="n">
-        <v>1492</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>2832</v>
+        <v>1908</v>
       </c>
       <c r="D6" t="n">
-        <v>832</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>1031</v>
+        <v>859</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3594</v>
+        <v>5190</v>
       </c>
       <c r="C2" t="n">
-        <v>11024</v>
+        <v>9841</v>
       </c>
       <c r="D2" t="n">
-        <v>18029</v>
+        <v>20577</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3333</v>
+        <v>3504</v>
       </c>
       <c r="C3" t="n">
-        <v>4637</v>
+        <v>4691</v>
       </c>
       <c r="D3" t="n">
-        <v>11701</v>
+        <v>13868</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>2402</v>
       </c>
       <c r="C4" t="n">
-        <v>5931</v>
+        <v>5056</v>
       </c>
       <c r="D4" t="n">
-        <v>5332</v>
+        <v>7467</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1484</v>
+        <v>1343</v>
       </c>
       <c r="C5" t="n">
-        <v>5552</v>
+        <v>4144</v>
       </c>
       <c r="D5" t="n">
-        <v>1945</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>759</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>3883</v>
+        <v>2634</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>1948</v>
+        <v>1403</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>678</v>
+        <v>591</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>

--- a/output/yearly_population_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_89_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5541</v>
+        <v>4880</v>
       </c>
       <c r="C2" t="n">
-        <v>9151</v>
+        <v>7644</v>
       </c>
       <c r="D2" t="n">
-        <v>32394</v>
+        <v>23344</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3510</v>
+        <v>3201</v>
       </c>
       <c r="C3" t="n">
-        <v>6322</v>
+        <v>6464</v>
       </c>
       <c r="D3" t="n">
-        <v>13879</v>
+        <v>11675</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2509</v>
+        <v>2767</v>
       </c>
       <c r="C4" t="n">
-        <v>4761</v>
+        <v>6565</v>
       </c>
       <c r="D4" t="n">
-        <v>8274</v>
+        <v>6029</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1599</v>
+        <v>1837</v>
       </c>
       <c r="C5" t="n">
-        <v>4513</v>
+        <v>6505</v>
       </c>
       <c r="D5" t="n">
-        <v>3487</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>912</v>
+        <v>1020</v>
       </c>
       <c r="C6" t="n">
-        <v>3305</v>
+        <v>4320</v>
       </c>
       <c r="D6" t="n">
-        <v>1352</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>1993</v>
+        <v>2376</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>958</v>
+        <v>1045</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6532</v>
+        <v>5945</v>
       </c>
       <c r="C2" t="n">
-        <v>16391</v>
+        <v>10172</v>
       </c>
       <c r="D2" t="n">
-        <v>35602</v>
+        <v>30202</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3581</v>
+        <v>3197</v>
       </c>
       <c r="C3" t="n">
-        <v>6682</v>
+        <v>6162</v>
       </c>
       <c r="D3" t="n">
-        <v>15464</v>
+        <v>12402</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2530</v>
+        <v>2552</v>
       </c>
       <c r="C4" t="n">
-        <v>5396</v>
+        <v>6381</v>
       </c>
       <c r="D4" t="n">
-        <v>8937</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1749</v>
+        <v>1965</v>
       </c>
       <c r="C5" t="n">
-        <v>4487</v>
+        <v>6333</v>
       </c>
       <c r="D5" t="n">
-        <v>4082</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1092</v>
+        <v>1231</v>
       </c>
       <c r="C6" t="n">
-        <v>3806</v>
+        <v>5223</v>
       </c>
       <c r="D6" t="n">
-        <v>1661</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>561</v>
+        <v>616</v>
       </c>
       <c r="C7" t="n">
-        <v>2538</v>
+        <v>3170</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C8" t="n">
-        <v>1384</v>
+        <v>1592</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="D9" t="n">
         <v>318</v>
@@ -1206,10 +1206,10 @@
         <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6952</v>
+        <v>6557</v>
       </c>
       <c r="C2" t="n">
-        <v>17652</v>
+        <v>10222</v>
       </c>
       <c r="D2" t="n">
-        <v>31915</v>
+        <v>25194</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3855</v>
+        <v>3455</v>
       </c>
       <c r="C3" t="n">
-        <v>9361</v>
+        <v>6871</v>
       </c>
       <c r="D3" t="n">
-        <v>16890</v>
+        <v>13744</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2508</v>
+        <v>2393</v>
       </c>
       <c r="C4" t="n">
-        <v>5775</v>
+        <v>6096</v>
       </c>
       <c r="D4" t="n">
-        <v>9519</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1826</v>
+        <v>1959</v>
       </c>
       <c r="C5" t="n">
-        <v>4725</v>
+        <v>6220</v>
       </c>
       <c r="D5" t="n">
-        <v>4657</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1241</v>
+        <v>1390</v>
       </c>
       <c r="C6" t="n">
-        <v>4047</v>
+        <v>5554</v>
       </c>
       <c r="D6" t="n">
-        <v>1948</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>685</v>
+        <v>756</v>
       </c>
       <c r="C7" t="n">
-        <v>3009</v>
+        <v>3922</v>
       </c>
       <c r="D7" t="n">
-        <v>891</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C8" t="n">
-        <v>1810</v>
+        <v>2163</v>
       </c>
       <c r="D8" t="n">
-        <v>498</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>913</v>
+        <v>999</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6455</v>
+        <v>6076</v>
       </c>
       <c r="C2" t="n">
-        <v>12144</v>
+        <v>7196</v>
       </c>
       <c r="D2" t="n">
-        <v>26342</v>
+        <v>20814</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4534</v>
+        <v>4158</v>
       </c>
       <c r="C3" t="n">
-        <v>13402</v>
+        <v>10210</v>
       </c>
       <c r="D3" t="n">
-        <v>18327</v>
+        <v>14770</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1687</v>
+        <v>1810</v>
       </c>
       <c r="C4" t="n">
-        <v>7640</v>
+        <v>9189</v>
       </c>
       <c r="D4" t="n">
-        <v>9432</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1146</v>
+        <v>1284</v>
       </c>
       <c r="C5" t="n">
-        <v>3966</v>
+        <v>5442</v>
       </c>
       <c r="D5" t="n">
-        <v>3160</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>632</v>
+        <v>698</v>
       </c>
       <c r="C6" t="n">
-        <v>2948</v>
+        <v>3843</v>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>1773</v>
+        <v>2119</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>894</v>
+        <v>979</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3939</v>
+        <v>3711</v>
       </c>
       <c r="C2" t="n">
-        <v>5617</v>
+        <v>4481</v>
       </c>
       <c r="D2" t="n">
-        <v>18394</v>
+        <v>14323</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4602</v>
+        <v>4269</v>
       </c>
       <c r="C3" t="n">
-        <v>11676</v>
+        <v>8073</v>
       </c>
       <c r="D3" t="n">
-        <v>18537</v>
+        <v>14883</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2367</v>
+        <v>2341</v>
       </c>
       <c r="C4" t="n">
-        <v>10300</v>
+        <v>9811</v>
       </c>
       <c r="D4" t="n">
-        <v>10516</v>
+        <v>8057</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1414</v>
       </c>
       <c r="C5" t="n">
-        <v>5555</v>
+        <v>7064</v>
       </c>
       <c r="D5" t="n">
-        <v>3937</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>743</v>
+        <v>821</v>
       </c>
       <c r="C6" t="n">
-        <v>3470</v>
+        <v>4563</v>
       </c>
       <c r="D6" t="n">
-        <v>1085</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>2210</v>
+        <v>2744</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>1167</v>
+        <v>1287</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>207</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3682</v>
+        <v>3359</v>
       </c>
       <c r="C2" t="n">
-        <v>6173</v>
+        <v>5009</v>
       </c>
       <c r="D2" t="n">
-        <v>18169</v>
+        <v>16237</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3644</v>
+        <v>3399</v>
       </c>
       <c r="C3" t="n">
-        <v>7851</v>
+        <v>5667</v>
       </c>
       <c r="D3" t="n">
-        <v>17271</v>
+        <v>13806</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2818</v>
+        <v>2711</v>
       </c>
       <c r="C4" t="n">
-        <v>10746</v>
+        <v>8866</v>
       </c>
       <c r="D4" t="n">
-        <v>11505</v>
+        <v>8926</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1532</v>
+        <v>1600</v>
       </c>
       <c r="C5" t="n">
-        <v>7679</v>
+        <v>8156</v>
       </c>
       <c r="D5" t="n">
-        <v>4827</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>967</v>
       </c>
       <c r="C6" t="n">
-        <v>4338</v>
+        <v>5600</v>
       </c>
       <c r="D6" t="n">
-        <v>1481</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="C7" t="n">
-        <v>2761</v>
+        <v>3536</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>1586</v>
+        <v>1870</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>706</v>
+        <v>754</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2230</v>
+        <v>2049</v>
       </c>
       <c r="C2" t="n">
-        <v>2981</v>
+        <v>2450</v>
       </c>
       <c r="D2" t="n">
-        <v>12682</v>
+        <v>11330</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3527</v>
+        <v>3273</v>
       </c>
       <c r="C3" t="n">
-        <v>7025</v>
+        <v>5302</v>
       </c>
       <c r="D3" t="n">
-        <v>16977</v>
+        <v>13749</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3084</v>
+        <v>2982</v>
       </c>
       <c r="C4" t="n">
-        <v>10740</v>
+        <v>8549</v>
       </c>
       <c r="D4" t="n">
-        <v>12252</v>
+        <v>9538</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1570</v>
+        <v>1662</v>
       </c>
       <c r="C5" t="n">
-        <v>9437</v>
+        <v>9603</v>
       </c>
       <c r="D5" t="n">
-        <v>5078</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>780</v>
       </c>
       <c r="C6" t="n">
-        <v>5168</v>
+        <v>6595</v>
       </c>
       <c r="D6" t="n">
-        <v>1439</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2873</v>
+        <v>3569</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1158</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2217</v>
+        <v>3259</v>
       </c>
       <c r="C2" t="n">
-        <v>7912</v>
+        <v>8741</v>
       </c>
       <c r="D2" t="n">
-        <v>16937</v>
+        <v>10411</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2576</v>
+        <v>2384</v>
       </c>
       <c r="C3" t="n">
-        <v>4719</v>
+        <v>3607</v>
       </c>
       <c r="D3" t="n">
-        <v>15313</v>
+        <v>12537</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2876</v>
+        <v>2711</v>
       </c>
       <c r="C4" t="n">
-        <v>8840</v>
+        <v>6957</v>
       </c>
       <c r="D4" t="n">
-        <v>12605</v>
+        <v>9894</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1908</v>
+        <v>1948</v>
       </c>
       <c r="C5" t="n">
-        <v>9894</v>
+        <v>9040</v>
       </c>
       <c r="D5" t="n">
-        <v>5956</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>924</v>
+        <v>1009</v>
       </c>
       <c r="C6" t="n">
-        <v>6894</v>
+        <v>7814</v>
       </c>
       <c r="D6" t="n">
-        <v>1923</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>3805</v>
+        <v>4759</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1768</v>
+        <v>2117</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1553</v>
+        <v>2175</v>
       </c>
       <c r="C2" t="n">
-        <v>4296</v>
+        <v>5558</v>
       </c>
       <c r="D2" t="n">
-        <v>12627</v>
+        <v>7813</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2165</v>
+        <v>2328</v>
       </c>
       <c r="C3" t="n">
-        <v>5439</v>
+        <v>5049</v>
       </c>
       <c r="D3" t="n">
-        <v>14686</v>
+        <v>11636</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2550</v>
+        <v>2413</v>
       </c>
       <c r="C4" t="n">
-        <v>7243</v>
+        <v>5694</v>
       </c>
       <c r="D4" t="n">
-        <v>12680</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="C5" t="n">
-        <v>9703</v>
+        <v>8479</v>
       </c>
       <c r="D5" t="n">
-        <v>6591</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1072</v>
+        <v>1172</v>
       </c>
       <c r="C6" t="n">
-        <v>8051</v>
+        <v>8499</v>
       </c>
       <c r="D6" t="n">
-        <v>2247</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>4760</v>
+        <v>5725</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2235</v>
+        <v>2748</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>621</v>
+        <v>679</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3326</v>
+        <v>2797</v>
       </c>
       <c r="C2" t="n">
-        <v>4810</v>
+        <v>11295</v>
       </c>
       <c r="D2" t="n">
-        <v>18579</v>
+        <v>15154</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1652</v>
+        <v>1915</v>
       </c>
       <c r="C3" t="n">
-        <v>4471</v>
+        <v>4674</v>
       </c>
       <c r="D3" t="n">
-        <v>13538</v>
+        <v>10544</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2104</v>
+        <v>2092</v>
       </c>
       <c r="C4" t="n">
-        <v>6364</v>
+        <v>5309</v>
       </c>
       <c r="D4" t="n">
-        <v>12564</v>
+        <v>9834</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2061</v>
+        <v>1996</v>
       </c>
       <c r="C5" t="n">
-        <v>8556</v>
+        <v>7206</v>
       </c>
       <c r="D5" t="n">
-        <v>7087</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1281</v>
+        <v>1364</v>
       </c>
       <c r="C6" t="n">
-        <v>8589</v>
+        <v>8421</v>
       </c>
       <c r="D6" t="n">
-        <v>2760</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="C7" t="n">
-        <v>5919</v>
+        <v>6784</v>
       </c>
       <c r="D7" t="n">
-        <v>939</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>3097</v>
+        <v>3738</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1111</v>
+        <v>1334</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3711,7 +3711,7 @@
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4607</v>
+        <v>5409</v>
       </c>
       <c r="C2" t="n">
-        <v>9511</v>
+        <v>10551</v>
       </c>
       <c r="D2" t="n">
-        <v>21436</v>
+        <v>12978</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2429</v>
+        <v>2044</v>
       </c>
       <c r="C2" t="n">
-        <v>2847</v>
+        <v>6597</v>
       </c>
       <c r="D2" t="n">
-        <v>13822</v>
+        <v>11274</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2346</v>
+        <v>2528</v>
       </c>
       <c r="C3" t="n">
-        <v>5010</v>
+        <v>6522</v>
       </c>
       <c r="D3" t="n">
-        <v>15001</v>
+        <v>11726</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>2913</v>
       </c>
       <c r="C4" t="n">
-        <v>9266</v>
+        <v>7852</v>
       </c>
       <c r="D4" t="n">
-        <v>12797</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1202</v>
+        <v>1278</v>
       </c>
       <c r="C5" t="n">
-        <v>12241</v>
+        <v>11332</v>
       </c>
       <c r="D5" t="n">
-        <v>6482</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="C6" t="n">
-        <v>7315</v>
+        <v>8133</v>
       </c>
       <c r="D6" t="n">
-        <v>2135</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3035</v>
+        <v>3663</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1088</v>
+        <v>1307</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4319,7 +4319,7 @@
         <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6662</v>
+        <v>6250</v>
       </c>
       <c r="C2" t="n">
-        <v>5323</v>
+        <v>5157</v>
       </c>
       <c r="D2" t="n">
-        <v>23998</v>
+        <v>13038</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1958</v>
+        <v>2299</v>
       </c>
       <c r="C3" t="n">
-        <v>4793</v>
+        <v>5317</v>
       </c>
       <c r="D3" t="n">
-        <v>4240</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="4">
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4592</v>
+        <v>5322</v>
       </c>
       <c r="C2" t="n">
-        <v>6588</v>
+        <v>10183</v>
       </c>
       <c r="D2" t="n">
-        <v>21300</v>
+        <v>17352</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3535</v>
+        <v>3509</v>
       </c>
       <c r="C3" t="n">
-        <v>4392</v>
+        <v>4507</v>
       </c>
       <c r="D3" t="n">
-        <v>7247</v>
+        <v>4328</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>885</v>
+        <v>1033</v>
       </c>
       <c r="C4" t="n">
-        <v>2852</v>
+        <v>3159</v>
       </c>
       <c r="D4" t="n">
-        <v>2035</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4465</v>
+        <v>6255</v>
       </c>
       <c r="C2" t="n">
-        <v>7913</v>
+        <v>11352</v>
       </c>
       <c r="D2" t="n">
-        <v>33339</v>
+        <v>18907</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3336</v>
+        <v>3610</v>
       </c>
       <c r="C3" t="n">
-        <v>4827</v>
+        <v>6580</v>
       </c>
       <c r="D3" t="n">
-        <v>8973</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1875</v>
+        <v>1931</v>
       </c>
       <c r="C4" t="n">
-        <v>3622</v>
+        <v>3856</v>
       </c>
       <c r="D4" t="n">
-        <v>2973</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="C5" t="n">
-        <v>1657</v>
+        <v>1824</v>
       </c>
       <c r="D5" t="n">
-        <v>1302</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4910</v>
+        <v>5551</v>
       </c>
       <c r="C2" t="n">
-        <v>8909</v>
+        <v>12038</v>
       </c>
       <c r="D2" t="n">
-        <v>28798</v>
+        <v>17818</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3177</v>
+        <v>3962</v>
       </c>
       <c r="C3" t="n">
-        <v>5566</v>
+        <v>7865</v>
       </c>
       <c r="D3" t="n">
-        <v>12044</v>
+        <v>7617</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2186</v>
+        <v>2319</v>
       </c>
       <c r="C4" t="n">
-        <v>4148</v>
+        <v>5240</v>
       </c>
       <c r="D4" t="n">
-        <v>3977</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>937</v>
+        <v>991</v>
       </c>
       <c r="C5" t="n">
-        <v>2641</v>
+        <v>2839</v>
       </c>
       <c r="D5" t="n">
-        <v>1538</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="C6" t="n">
-        <v>978</v>
+        <v>1057</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5997</v>
+        <v>6560</v>
       </c>
       <c r="C2" t="n">
-        <v>6239</v>
+        <v>11411</v>
       </c>
       <c r="D2" t="n">
-        <v>24247</v>
+        <v>26470</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2904</v>
+        <v>3473</v>
       </c>
       <c r="C3" t="n">
-        <v>5936</v>
+        <v>8161</v>
       </c>
       <c r="D3" t="n">
-        <v>12929</v>
+        <v>8120</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1644</v>
+        <v>1919</v>
       </c>
       <c r="C4" t="n">
-        <v>4021</v>
+        <v>5410</v>
       </c>
       <c r="D4" t="n">
-        <v>4648</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>804</v>
+        <v>852</v>
       </c>
       <c r="C5" t="n">
-        <v>2467</v>
+        <v>2983</v>
       </c>
       <c r="D5" t="n">
-        <v>1537</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>1212</v>
+        <v>1305</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4878</v>
+        <v>4896</v>
       </c>
       <c r="C2" t="n">
-        <v>5542</v>
+        <v>5208</v>
       </c>
       <c r="D2" t="n">
-        <v>20063</v>
+        <v>20838</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3682</v>
+        <v>4149</v>
       </c>
       <c r="C3" t="n">
-        <v>5259</v>
+        <v>8636</v>
       </c>
       <c r="D3" t="n">
-        <v>13878</v>
+        <v>10605</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1986</v>
+        <v>2356</v>
       </c>
       <c r="C4" t="n">
-        <v>5038</v>
+        <v>6934</v>
       </c>
       <c r="D4" t="n">
-        <v>6176</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1079</v>
+        <v>1226</v>
       </c>
       <c r="C5" t="n">
-        <v>3325</v>
+        <v>4318</v>
       </c>
       <c r="D5" t="n">
-        <v>2072</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>1908</v>
+        <v>2210</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>859</v>
+        <v>922</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>209</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5190</v>
+        <v>4056</v>
       </c>
       <c r="C2" t="n">
-        <v>9841</v>
+        <v>8962</v>
       </c>
       <c r="D2" t="n">
-        <v>20577</v>
+        <v>18689</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3504</v>
+        <v>3718</v>
       </c>
       <c r="C3" t="n">
-        <v>4691</v>
+        <v>5939</v>
       </c>
       <c r="D3" t="n">
-        <v>13868</v>
+        <v>11413</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2402</v>
+        <v>2780</v>
       </c>
       <c r="C4" t="n">
-        <v>5056</v>
+        <v>7654</v>
       </c>
       <c r="D4" t="n">
-        <v>7467</v>
+        <v>5092</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1343</v>
+        <v>1546</v>
       </c>
       <c r="C5" t="n">
-        <v>4144</v>
+        <v>5634</v>
       </c>
       <c r="D5" t="n">
-        <v>2757</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>706</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>2634</v>
+        <v>3278</v>
       </c>
       <c r="D6" t="n">
-        <v>1109</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1403</v>
+        <v>1577</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_89_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4880</v>
+        <v>1356</v>
       </c>
       <c r="C2" t="n">
-        <v>7644</v>
+        <v>2059</v>
       </c>
       <c r="D2" t="n">
-        <v>23344</v>
+        <v>11093</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3201</v>
+        <v>2381</v>
       </c>
       <c r="C3" t="n">
-        <v>6464</v>
+        <v>5995</v>
       </c>
       <c r="D3" t="n">
-        <v>11675</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2767</v>
+        <v>1609</v>
       </c>
       <c r="C4" t="n">
-        <v>6565</v>
+        <v>7873</v>
       </c>
       <c r="D4" t="n">
-        <v>6029</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1837</v>
+        <v>790</v>
       </c>
       <c r="C5" t="n">
-        <v>6505</v>
+        <v>4462</v>
       </c>
       <c r="D5" t="n">
-        <v>2410</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1020</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>4320</v>
+        <v>1463</v>
       </c>
       <c r="D6" t="n">
-        <v>1117</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>2376</v>
+        <v>591</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1045</v>
+        <v>340</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>424</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5945</v>
+        <v>1010</v>
       </c>
       <c r="C2" t="n">
-        <v>10172</v>
+        <v>6058</v>
       </c>
       <c r="D2" t="n">
-        <v>30202</v>
+        <v>12838</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3197</v>
+        <v>1606</v>
       </c>
       <c r="C3" t="n">
-        <v>6162</v>
+        <v>3389</v>
       </c>
       <c r="D3" t="n">
-        <v>12402</v>
+        <v>10244</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2552</v>
+        <v>1707</v>
       </c>
       <c r="C4" t="n">
-        <v>6381</v>
+        <v>6663</v>
       </c>
       <c r="D4" t="n">
-        <v>6655</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1965</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="n">
-        <v>6333</v>
+        <v>6245</v>
       </c>
       <c r="D5" t="n">
-        <v>2892</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1231</v>
+        <v>479</v>
       </c>
       <c r="C6" t="n">
-        <v>5223</v>
+        <v>2987</v>
       </c>
       <c r="D6" t="n">
-        <v>1277</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>616</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>3170</v>
+        <v>1023</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1592</v>
+        <v>458</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>663</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6557</v>
+        <v>522</v>
       </c>
       <c r="C2" t="n">
-        <v>10222</v>
+        <v>2480</v>
       </c>
       <c r="D2" t="n">
-        <v>25194</v>
+        <v>8664</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3455</v>
+        <v>1385</v>
       </c>
       <c r="C3" t="n">
-        <v>6871</v>
+        <v>4310</v>
       </c>
       <c r="D3" t="n">
-        <v>13744</v>
+        <v>10297</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2393</v>
+        <v>1863</v>
       </c>
       <c r="C4" t="n">
-        <v>6096</v>
+        <v>5843</v>
       </c>
       <c r="D4" t="n">
-        <v>7280</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1959</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>6220</v>
+        <v>7134</v>
       </c>
       <c r="D5" t="n">
-        <v>3282</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1390</v>
+        <v>380</v>
       </c>
       <c r="C6" t="n">
-        <v>5554</v>
+        <v>3967</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>756</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>3922</v>
+        <v>1024</v>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2163</v>
+        <v>477</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>999</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>419</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6076</v>
+        <v>475</v>
       </c>
       <c r="C2" t="n">
-        <v>7196</v>
+        <v>5493</v>
       </c>
       <c r="D2" t="n">
-        <v>20814</v>
+        <v>12650</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4158</v>
+        <v>845</v>
       </c>
       <c r="C3" t="n">
-        <v>10210</v>
+        <v>2929</v>
       </c>
       <c r="D3" t="n">
-        <v>14770</v>
+        <v>9323</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1810</v>
+        <v>1451</v>
       </c>
       <c r="C4" t="n">
-        <v>9189</v>
+        <v>4938</v>
       </c>
       <c r="D4" t="n">
-        <v>7020</v>
+        <v>7088</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="C5" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="D5" t="n">
-        <v>2329</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>698</v>
+        <v>598</v>
       </c>
       <c r="C6" t="n">
-        <v>3843</v>
+        <v>5484</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>2119</v>
+        <v>2399</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>979</v>
+        <v>721</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3711</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>4481</v>
+        <v>3684</v>
       </c>
       <c r="D2" t="n">
-        <v>14323</v>
+        <v>8685</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4269</v>
+        <v>613</v>
       </c>
       <c r="C3" t="n">
-        <v>8073</v>
+        <v>3734</v>
       </c>
       <c r="D3" t="n">
-        <v>14883</v>
+        <v>9339</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2341</v>
+        <v>1144</v>
       </c>
       <c r="C4" t="n">
-        <v>9811</v>
+        <v>4013</v>
       </c>
       <c r="D4" t="n">
-        <v>8057</v>
+        <v>7283</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1414</v>
+        <v>1315</v>
       </c>
       <c r="C5" t="n">
-        <v>7064</v>
+        <v>5912</v>
       </c>
       <c r="D5" t="n">
-        <v>2843</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>821</v>
+        <v>748</v>
       </c>
       <c r="C6" t="n">
-        <v>4563</v>
+        <v>6124</v>
       </c>
       <c r="D6" t="n">
-        <v>901</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>191</v>
       </c>
       <c r="C7" t="n">
-        <v>2744</v>
+        <v>3499</v>
       </c>
       <c r="D7" t="n">
-        <v>509</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1287</v>
+        <v>1146</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3359</v>
+        <v>989</v>
       </c>
       <c r="C2" t="n">
-        <v>5009</v>
+        <v>6577</v>
       </c>
       <c r="D2" t="n">
-        <v>16237</v>
+        <v>10931</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3399</v>
+        <v>390</v>
       </c>
       <c r="C3" t="n">
-        <v>5667</v>
+        <v>3253</v>
       </c>
       <c r="D3" t="n">
-        <v>13806</v>
+        <v>8602</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2711</v>
+        <v>804</v>
       </c>
       <c r="C4" t="n">
-        <v>8866</v>
+        <v>3790</v>
       </c>
       <c r="D4" t="n">
-        <v>8926</v>
+        <v>7416</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1600</v>
+        <v>1155</v>
       </c>
       <c r="C5" t="n">
-        <v>8156</v>
+        <v>4934</v>
       </c>
       <c r="D5" t="n">
-        <v>3557</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>967</v>
+        <v>905</v>
       </c>
       <c r="C6" t="n">
-        <v>5600</v>
+        <v>5968</v>
       </c>
       <c r="D6" t="n">
-        <v>1168</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>3536</v>
+        <v>4689</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>1870</v>
+        <v>2125</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>754</v>
+        <v>715</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2049</v>
+        <v>656</v>
       </c>
       <c r="C2" t="n">
-        <v>2450</v>
+        <v>3368</v>
       </c>
       <c r="D2" t="n">
-        <v>11330</v>
+        <v>7870</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3273</v>
+        <v>679</v>
       </c>
       <c r="C3" t="n">
-        <v>5302</v>
+        <v>4454</v>
       </c>
       <c r="D3" t="n">
-        <v>13749</v>
+        <v>9334</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2982</v>
+        <v>1443</v>
       </c>
       <c r="C4" t="n">
-        <v>8549</v>
+        <v>5384</v>
       </c>
       <c r="D4" t="n">
-        <v>9538</v>
+        <v>7804</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1662</v>
+        <v>932</v>
       </c>
       <c r="C5" t="n">
-        <v>9603</v>
+        <v>7821</v>
       </c>
       <c r="D5" t="n">
-        <v>3763</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>780</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>6595</v>
+        <v>6174</v>
       </c>
       <c r="D6" t="n">
-        <v>1155</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>3569</v>
+        <v>2082</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>700</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3259</v>
+        <v>330</v>
       </c>
       <c r="C2" t="n">
-        <v>8741</v>
+        <v>2484</v>
       </c>
       <c r="D2" t="n">
-        <v>10411</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2384</v>
+        <v>567</v>
       </c>
       <c r="C3" t="n">
-        <v>3607</v>
+        <v>3424</v>
       </c>
       <c r="D3" t="n">
-        <v>12537</v>
+        <v>8428</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2711</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>6957</v>
+        <v>4647</v>
       </c>
       <c r="D4" t="n">
-        <v>9894</v>
+        <v>7597</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1948</v>
+        <v>837</v>
       </c>
       <c r="C5" t="n">
-        <v>9040</v>
+        <v>5895</v>
       </c>
       <c r="D5" t="n">
-        <v>4480</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1009</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>7814</v>
+        <v>5696</v>
       </c>
       <c r="D6" t="n">
-        <v>1501</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>4759</v>
+        <v>2835</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>2117</v>
+        <v>813</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>617</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2175</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>5558</v>
+        <v>5017</v>
       </c>
       <c r="D2" t="n">
-        <v>7813</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2328</v>
+        <v>378</v>
       </c>
       <c r="C3" t="n">
-        <v>5049</v>
+        <v>2527</v>
       </c>
       <c r="D3" t="n">
-        <v>11636</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2413</v>
+        <v>650</v>
       </c>
       <c r="C4" t="n">
-        <v>5694</v>
+        <v>3845</v>
       </c>
       <c r="D4" t="n">
-        <v>10018</v>
+        <v>7525</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2069</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>8479</v>
+        <v>5134</v>
       </c>
       <c r="D5" t="n">
-        <v>5001</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1172</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>8499</v>
+        <v>5736</v>
       </c>
       <c r="D6" t="n">
-        <v>1741</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>5725</v>
+        <v>4347</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>2748</v>
+        <v>1811</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>529</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2797</v>
+        <v>339</v>
       </c>
       <c r="C2" t="n">
-        <v>11295</v>
+        <v>8365</v>
       </c>
       <c r="D2" t="n">
-        <v>15154</v>
+        <v>14304</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1915</v>
+        <v>353</v>
       </c>
       <c r="C3" t="n">
-        <v>4674</v>
+        <v>3339</v>
       </c>
       <c r="D3" t="n">
-        <v>10544</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2092</v>
+        <v>458</v>
       </c>
       <c r="C4" t="n">
-        <v>5309</v>
+        <v>3032</v>
       </c>
       <c r="D4" t="n">
-        <v>9834</v>
+        <v>7276</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1996</v>
+        <v>671</v>
       </c>
       <c r="C5" t="n">
-        <v>7206</v>
+        <v>4358</v>
       </c>
       <c r="D5" t="n">
-        <v>5523</v>
+        <v>4932</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1364</v>
+        <v>594</v>
       </c>
       <c r="C6" t="n">
-        <v>8421</v>
+        <v>5373</v>
       </c>
       <c r="D6" t="n">
-        <v>2125</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>471</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>6784</v>
+        <v>5025</v>
       </c>
       <c r="D7" t="n">
-        <v>806</v>
+        <v>955</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>3738</v>
+        <v>3003</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1334</v>
+        <v>1106</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5409</v>
+        <v>4293</v>
       </c>
       <c r="C2" t="n">
-        <v>10551</v>
+        <v>6746</v>
       </c>
       <c r="D2" t="n">
-        <v>12978</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2044</v>
+        <v>663</v>
       </c>
       <c r="C2" t="n">
-        <v>6597</v>
+        <v>18996</v>
       </c>
       <c r="D2" t="n">
-        <v>11274</v>
+        <v>17897</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2528</v>
+        <v>288</v>
       </c>
       <c r="C3" t="n">
-        <v>6522</v>
+        <v>4948</v>
       </c>
       <c r="D3" t="n">
-        <v>11726</v>
+        <v>7642</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2913</v>
+        <v>360</v>
       </c>
       <c r="C4" t="n">
-        <v>7852</v>
+        <v>3087</v>
       </c>
       <c r="D4" t="n">
-        <v>10010</v>
+        <v>6964</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>534</v>
       </c>
       <c r="C5" t="n">
-        <v>11332</v>
+        <v>3643</v>
       </c>
       <c r="D5" t="n">
-        <v>5038</v>
+        <v>5164</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>435</v>
+        <v>587</v>
       </c>
       <c r="C6" t="n">
-        <v>8133</v>
+        <v>4862</v>
       </c>
       <c r="D6" t="n">
-        <v>1707</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="C7" t="n">
-        <v>3663</v>
+        <v>5127</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>1307</v>
+        <v>3873</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>1886</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>637</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6250</v>
+        <v>5797</v>
       </c>
       <c r="C2" t="n">
-        <v>5157</v>
+        <v>6008</v>
       </c>
       <c r="D2" t="n">
-        <v>13038</v>
+        <v>15617</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2299</v>
+        <v>1419</v>
       </c>
       <c r="C3" t="n">
-        <v>5317</v>
+        <v>2664</v>
       </c>
       <c r="D3" t="n">
-        <v>2819</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5322</v>
+        <v>3376</v>
       </c>
       <c r="C2" t="n">
-        <v>10183</v>
+        <v>6615</v>
       </c>
       <c r="D2" t="n">
-        <v>17352</v>
+        <v>13558</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3509</v>
+        <v>3060</v>
       </c>
       <c r="C3" t="n">
-        <v>4507</v>
+        <v>4019</v>
       </c>
       <c r="D3" t="n">
-        <v>4328</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1033</v>
+        <v>682</v>
       </c>
       <c r="C4" t="n">
-        <v>3159</v>
+        <v>1709</v>
       </c>
       <c r="D4" t="n">
-        <v>1749</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6255</v>
+        <v>2978</v>
       </c>
       <c r="C2" t="n">
-        <v>11352</v>
+        <v>5918</v>
       </c>
       <c r="D2" t="n">
-        <v>18907</v>
+        <v>18819</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3610</v>
+        <v>2655</v>
       </c>
       <c r="C3" t="n">
-        <v>6580</v>
+        <v>4761</v>
       </c>
       <c r="D3" t="n">
-        <v>6100</v>
+        <v>5165</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1931</v>
+        <v>1640</v>
       </c>
       <c r="C4" t="n">
-        <v>3856</v>
+        <v>3070</v>
       </c>
       <c r="D4" t="n">
-        <v>2190</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>476</v>
+        <v>342</v>
       </c>
       <c r="C5" t="n">
-        <v>1824</v>
+        <v>1081</v>
       </c>
       <c r="D5" t="n">
-        <v>1250</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5551</v>
+        <v>2903</v>
       </c>
       <c r="C2" t="n">
-        <v>12038</v>
+        <v>10356</v>
       </c>
       <c r="D2" t="n">
-        <v>17818</v>
+        <v>23944</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3962</v>
+        <v>2322</v>
       </c>
       <c r="C3" t="n">
-        <v>7865</v>
+        <v>4668</v>
       </c>
       <c r="D3" t="n">
-        <v>7617</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2319</v>
+        <v>1857</v>
       </c>
       <c r="C4" t="n">
-        <v>5240</v>
+        <v>3980</v>
       </c>
       <c r="D4" t="n">
-        <v>2836</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>991</v>
+        <v>838</v>
       </c>
       <c r="C5" t="n">
-        <v>2839</v>
+        <v>2165</v>
       </c>
       <c r="D5" t="n">
-        <v>1362</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="C6" t="n">
-        <v>1057</v>
+        <v>697</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6560</v>
+        <v>2282</v>
       </c>
       <c r="C2" t="n">
-        <v>11411</v>
+        <v>5766</v>
       </c>
       <c r="D2" t="n">
-        <v>26470</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3473</v>
+        <v>2143</v>
       </c>
       <c r="C3" t="n">
-        <v>8161</v>
+        <v>6649</v>
       </c>
       <c r="D3" t="n">
-        <v>8120</v>
+        <v>9064</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1919</v>
+        <v>1803</v>
       </c>
       <c r="C4" t="n">
-        <v>5410</v>
+        <v>4273</v>
       </c>
       <c r="D4" t="n">
-        <v>3158</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>852</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="n">
-        <v>2983</v>
+        <v>3078</v>
       </c>
       <c r="D5" t="n">
-        <v>1265</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>296</v>
+        <v>448</v>
       </c>
       <c r="C6" t="n">
-        <v>1305</v>
+        <v>1429</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4896</v>
+        <v>3011</v>
       </c>
       <c r="C2" t="n">
-        <v>5208</v>
+        <v>8169</v>
       </c>
       <c r="D2" t="n">
-        <v>20838</v>
+        <v>19784</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4149</v>
+        <v>1825</v>
       </c>
       <c r="C3" t="n">
-        <v>8636</v>
+        <v>5427</v>
       </c>
       <c r="D3" t="n">
-        <v>10605</v>
+        <v>9922</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2356</v>
+        <v>1697</v>
       </c>
       <c r="C4" t="n">
-        <v>6934</v>
+        <v>5415</v>
       </c>
       <c r="D4" t="n">
-        <v>4062</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1226</v>
+        <v>1282</v>
       </c>
       <c r="C5" t="n">
-        <v>4318</v>
+        <v>3580</v>
       </c>
       <c r="D5" t="n">
-        <v>1577</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>522</v>
+        <v>698</v>
       </c>
       <c r="C6" t="n">
-        <v>2210</v>
+        <v>2221</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>922</v>
+        <v>944</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4056</v>
+        <v>2688</v>
       </c>
       <c r="C2" t="n">
-        <v>8962</v>
+        <v>4966</v>
       </c>
       <c r="D2" t="n">
-        <v>18689</v>
+        <v>15447</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3718</v>
+        <v>2720</v>
       </c>
       <c r="C3" t="n">
-        <v>5939</v>
+        <v>8545</v>
       </c>
       <c r="D3" t="n">
-        <v>11413</v>
+        <v>11027</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2780</v>
+        <v>1184</v>
       </c>
       <c r="C4" t="n">
-        <v>7654</v>
+        <v>6867</v>
       </c>
       <c r="D4" t="n">
-        <v>5092</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1546</v>
+        <v>644</v>
       </c>
       <c r="C5" t="n">
-        <v>5634</v>
+        <v>2176</v>
       </c>
       <c r="D5" t="n">
-        <v>1982</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>3278</v>
+        <v>925</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>1577</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>620</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
